--- a/題庫/OSH_ENV_QuizBank.xlsx
+++ b/題庫/OSH_ENV_QuizBank.xlsx
@@ -2223,7 +2223,11 @@
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>（法規資料庫無此法規代碼：行政方案或尚未立法）</t>
+        </is>
+      </c>
       <c r="H49" t="n">
         <v>2</v>
       </c>
@@ -2639,7 +2643,11 @@
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>（法規資料庫無此法規代碼：行政方案或尚未立法）</t>
+        </is>
+      </c>
       <c r="H61" t="n">
         <v>1</v>
       </c>

--- a/題庫/OSH_ENV_QuizBank.xlsx
+++ b/題庫/OSH_ENV_QuizBank.xlsx
@@ -591,7 +591,11 @@
           <t>Labor Inspection Act</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>民國109年6月10日</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>https://law.moj.gov.tw/LawClass/LawAll.aspx?pcode=N0070001</t>
@@ -626,7 +630,11 @@
           <t>Enforcement Rules of the Labor Inspection Act</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>民國112年12月7日</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>https://law.moj.gov.tw/LawClass/LawAll.aspx?pcode=N0070004</t>
@@ -661,7 +669,11 @@
           <t>Act for Protecting Workers of Occupational Accidents</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>民國107年11月21日</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>https://law.moj.gov.tw/LawClass/LawAll.aspx?pcode=N0060041</t>
@@ -696,7 +708,11 @@
           <t>Enforcement Rules of the Act for Protecting Workers of Occupational Accidents</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>民國108年2月23日</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>https://law.moj.gov.tw/LawClass/LawAll.aspx?pcode=N0060045</t>
@@ -1082,7 +1098,11 @@
           <t>Standards for Visual Protection Facilities for Precision Work</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>民國103年6月30日</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>https://law.moj.gov.tw/LawClass/LawAll.aspx?pcode=N0060012</t>
@@ -1117,7 +1137,11 @@
           <t>Standards for Protective Measures for Heavy Physical Labor</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>民國103年6月30日</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>https://law.moj.gov.tw/LawClass/LawAll.aspx?pcode=N0060016</t>
@@ -1191,7 +1215,11 @@
           <t>Regulations for Accreditation and Management of Medical Institutions for Labor Health Examinations</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>民國111年8月12日</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>https://law.moj.gov.tw/LawClass/LawAll.aspx?pcode=N0060040</t>
@@ -1226,7 +1254,11 @@
           <t>Standards for Identifying Dangerous or Harmful Work Prohibited for Pregnant/Postpartum Women and Laborers under 18</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>民國114年11月20日</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>https://law.moj.gov.tw/LawClass/LawAll.aspx?pcode=N0060032</t>
@@ -1261,7 +1293,11 @@
           <t>Standards for Safety and Health Facilities for Female Laborers Working at Night</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>民國104年3月31日</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>https://law.moj.gov.tw/LawClass/LawAll.aspx?pcode=N0030011</t>
@@ -1296,7 +1332,11 @@
           <t>Regulations for Implementing Maternal Health Protection of Female Laborers</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>民國113年5月31日</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>https://law.moj.gov.tw/LawClass/LawAll.aspx?pcode=N0060065</t>
@@ -1331,7 +1371,11 @@
           <t>Standards for Prevention of Industrial Robot Hazards</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>民國107年2月14日</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>https://law.moj.gov.tw/LawClass/LawAll.aspx?pcode=N0060025</t>
@@ -1405,7 +1449,11 @@
           <t>Standards for Identifying Imminent Danger under Article 28 of the Labor Inspection Act</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>民國94年6月10日</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>https://law.moj.gov.tw/LawClass/LawAll.aspx?pcode=N0070016</t>
@@ -1440,10 +1488,14 @@
           <t>Directions for Selection of Outstanding OSH Units and Personnel</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>民國114年1月17日</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://law.isha.org.tw/ISHA_LAW/</t>
+          <t>https://laws.mol.gov.tw/FLAW/FLAWDAT01.aspx?id=FL015052</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -1475,10 +1527,14 @@
           <t>Directions for Handling Violations of the OSH Act and Labor Inspection Act</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>民國115年7月1日</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://law.isha.org.tw/ISHA_LAW/</t>
+          <t>https://laws.mol.gov.tw/FLAW/FLAWDAT01.aspx?id=FL024857</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -1510,10 +1566,14 @@
           <t>MOL Directions for Major Accident Notification and Inspection</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>民國110年9月</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://law.isha.org.tw/ISHA_LAW/</t>
+          <t>http://law.isha.org.tw/ISHA_LAW/Pages/LawList.aspx?Lawid=022</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -1545,7 +1605,11 @@
           <t>Rules for Accreditation and Management of OSH Consulting Institutions</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>民國113年10月31日</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>https://law.moj.gov.tw/LawClass/LawAll.aspx?pcode=N0060066</t>
@@ -1572,18 +1636,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>政府機關推動職業安全衛生業務績效評核及獎勵作業要點</t>
+          <t>政府機關推動職業安全衛生業務績效評核及獎勵辦法</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Directions for Performance Evaluation of Government OSH Promotion</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
+          <t>Regulations for Performance Evaluation and Rewards of Government OSH Promotion</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>民國103年11月27日</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://law.isha.org.tw/ISHA_LAW/</t>
+          <t>https://law.moj.gov.tw/LawClass/LawAll.aspx?pcode=N0060061</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -1615,7 +1683,11 @@
           <t>Regulations for Rewards and Subsidies to Promote OSH Culture</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>民國103年11月28日</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>https://law.moj.gov.tw/LawClass/LawAll.aspx?pcode=N0060035</t>
@@ -1689,10 +1761,14 @@
           <t>Directions for Designation of Laboratories for Specific Health Examination Items</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>民國112年5月22日</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://law.isha.org.tw/ISHA_LAW/</t>
+          <t>https://laws.mol.gov.tw/FLAW/FLAWDAT01.aspx?id=FL078462</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -1763,7 +1839,11 @@
           <t>Labor Occupational Accident Insurance and Protection Act</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>民國110年4月30日</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>https://law.moj.gov.tw/LawClass/LawAll.aspx?pcode=N0050031</t>
@@ -1837,7 +1917,11 @@
           <t>Air Pollution Control Act</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>民國107年8月1日</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>https://law.moj.gov.tw/LawClass/LawAll.aspx?pcode=O0020001</t>
@@ -1872,7 +1956,11 @@
           <t>Enforcement Rules of the Air Pollution Control Act</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>民國109年9月18日</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>https://law.moj.gov.tw/LawClass/LawAll.aspx?pcode=O0020002</t>
@@ -1907,7 +1995,11 @@
           <t>Regulations on Air Pollution Control Facilities for Construction Projects</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>民國110年10月18日</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>https://law.moj.gov.tw/LawClass/LawAll.aspx?pcode=O0020058</t>
@@ -1942,7 +2034,11 @@
           <t>Regulations on Control Facilities for Fugitive Particulate Pollutants from Stationary Sources</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>民國112年7月6日</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
           <t>https://law.moj.gov.tw/LawClass/LawAll.aspx?pcode=O0020078</t>
@@ -1977,7 +2073,11 @@
           <t>Noise Control Act</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>民國114年12月26日</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr">
         <is>
           <t>https://law.moj.gov.tw/LawClass/LawAll.aspx?pcode=O0030001</t>
@@ -2012,7 +2112,11 @@
           <t>Noise Control Standards</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>民國102年8月5日</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr">
         <is>
           <t>https://law.moj.gov.tw/LawClass/LawAll.aspx?pcode=O0030006</t>
@@ -2047,7 +2151,11 @@
           <t>Water Pollution Control Act</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>民國107年6月13日</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr">
         <is>
           <t>https://law.moj.gov.tw/LawClass/LawAll.aspx?pcode=O0040001</t>
@@ -2082,7 +2190,11 @@
           <t>Effluent Standards</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>民國113年12月18日</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr">
         <is>
           <t>https://law.moj.gov.tw/LawClass/LawAll.aspx?pcode=O0040004</t>
@@ -2117,7 +2229,11 @@
           <t>Regulations on Water Pollution Control Measures and Monitoring Reporting</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>民國115年4月20日</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr">
         <is>
           <t>https://law.moj.gov.tw/LawClass/LawAll.aspx?pcode=O0040054</t>
@@ -2152,7 +2268,11 @@
           <t>Waste Disposal Act</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>民國115年7月15日</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr">
         <is>
           <t>https://law.moj.gov.tw/LawClass/LawAll.aspx?pcode=O0050001</t>
@@ -2187,7 +2307,11 @@
           <t>Standards for Storage, Clearance and Disposal of Industrial Waste</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>民國112年11月1日</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr">
         <is>
           <t>https://law.moj.gov.tw/LawClass/LawAll.aspx?pcode=O0050005</t>
@@ -2222,10 +2346,14 @@
           <t>Construction Surplus Soil and Rock Disposal Program</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>民國113年5月15日</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>（法規資料庫無此法規代碼：行政方案或尚未立法）</t>
+          <t>https://glrs.moi.gov.tw/LawContent.aspx?id=FL003875</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -2257,7 +2385,11 @@
           <t>Environmental Impact Assessment Act</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>民國114年11月28日</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr">
         <is>
           <t>https://law.moj.gov.tw/LawClass/LawAll.aspx?pcode=O0090001</t>
@@ -2292,7 +2424,11 @@
           <t>Marine Pollution Control Act</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>民國112年5月31日</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr">
         <is>
           <t>https://law.moj.gov.tw/LawClass/LawAll.aspx?pcode=O0040026</t>
@@ -2327,7 +2463,11 @@
           <t>Coastal Zone Management Act</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>民國104年2月4日</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr">
         <is>
           <t>https://law.moj.gov.tw/LawClass/LawAll.aspx?pcode=D0070222</t>
@@ -2362,7 +2502,11 @@
           <t>Marine Conservation Act</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>民國113年7月31日</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr">
         <is>
           <t>https://law.moj.gov.tw/LawClass/LawAll.aspx?pcode=D0090073</t>
@@ -2397,7 +2541,11 @@
           <t>Wildlife Conservation Act</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>民國114年2月18日</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr">
         <is>
           <t>https://law.moj.gov.tw/LawClass/LawAll.aspx?pcode=M0120001</t>
@@ -2432,7 +2580,11 @@
           <t>Wetland Conservation Act</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>民國102年7月3日</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr">
         <is>
           <t>https://law.moj.gov.tw/LawClass/LawAll.aspx?pcode=D0070209</t>
@@ -2467,7 +2619,11 @@
           <t>Soil and Groundwater Pollution Remediation Act</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>民國99年2月3日</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr">
         <is>
           <t>https://law.moj.gov.tw/LawClass/LawAll.aspx?pcode=O0110001</t>
@@ -2502,7 +2658,11 @@
           <t>Toxic and Concerned Chemical Substances Control Act</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>民國108年1月16日</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr">
         <is>
           <t>https://law.moj.gov.tw/LawClass/LawAll.aspx?pcode=O0060012</t>
@@ -2537,7 +2697,11 @@
           <t>Basic Environment Act</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>民國91年12月11日</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr">
         <is>
           <t>https://law.moj.gov.tw/LawClass/LawAll.aspx?pcode=O0100001</t>
@@ -2572,7 +2736,11 @@
           <t>Climate Change Response Act</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>民國112年2月15日</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr">
         <is>
           <t>https://law.moj.gov.tw/LawClass/LawAll.aspx?pcode=O0020098</t>
@@ -2607,7 +2775,11 @@
           <t>Environmental Education Act</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>民國106年11月29日</t>
+        </is>
+      </c>
       <c r="G60" t="inlineStr">
         <is>
           <t>https://law.moj.gov.tw/LawClass/LawAll.aspx?pcode=O0120001</t>
@@ -2634,18 +2806,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>資源循環利用法</t>
+          <t>資源循環推動法</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Resource Recycling Act</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
+          <t>Resource Circulation Promotion Act</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>民國115年6月17日</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>（法規資料庫無此法規代碼：行政方案或尚未立法）</t>
+          <t>https://law.moj.gov.tw/LawClass/LawAll.aspx?pcode=O0050049</t>
         </is>
       </c>
       <c r="H61" t="n">
@@ -2677,7 +2853,11 @@
           <t>Public Nuisance Dispute Mediation Act</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>民國98年6月17日</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr">
         <is>
           <t>https://law.moj.gov.tw/LawClass/LawAll.aspx?pcode=O0080001</t>
